--- a/output/yearly_benthic_cover_iteration_61_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_61_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.69362843609312</v>
+        <v>45.33367885473822</v>
       </c>
       <c r="M2" t="n">
-        <v>98.41878516583745</v>
+        <v>98.97227603234384</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.88092500840142</v>
+        <v>88.00213157996774</v>
       </c>
       <c r="C3" t="n">
-        <v>45.83185663799506</v>
+        <v>45.90164001475909</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22842808144426</v>
+        <v>2.228686528836853</v>
       </c>
       <c r="E3" t="n">
-        <v>5.643159187188318</v>
+        <v>5.689582473511602</v>
       </c>
       <c r="F3" t="n">
-        <v>0.74280936048142</v>
+        <v>0.7428955096122843</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94101851956754</v>
+        <v>33.96398830154435</v>
       </c>
       <c r="H3" t="n">
-        <v>34.16923058214531</v>
+        <v>34.17319344216508</v>
       </c>
       <c r="I3" t="n">
-        <v>6.513720774565695</v>
+        <v>6.560688389220801</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642558503008875</v>
+        <v>4.643096935076777</v>
       </c>
       <c r="K3" t="n">
-        <v>12.11907499159857</v>
+        <v>11.99786842003226</v>
       </c>
       <c r="L3" t="n">
-        <v>48.81522745523196</v>
+        <v>48.86499183729869</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7661590848256</v>
+        <v>106.76450027209</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.9267539920434</v>
+        <v>86.95659500515561</v>
       </c>
       <c r="C4" t="n">
-        <v>42.50592757323539</v>
+        <v>42.49082295941807</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182117003429304</v>
+        <v>2.17761402821628</v>
       </c>
       <c r="E4" t="n">
-        <v>6.432453795822513</v>
+        <v>6.472320619925712</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443587316190001</v>
+        <v>0.7444557203256932</v>
       </c>
       <c r="G4" t="n">
-        <v>33.23565801470978</v>
+        <v>33.18567076286697</v>
       </c>
       <c r="H4" t="n">
-        <v>34.240501654474</v>
+        <v>34.24496313498189</v>
       </c>
       <c r="I4" t="n">
-        <v>5.439422719370055</v>
+        <v>5.478722486803479</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65224207261875</v>
+        <v>4.652848252035581</v>
       </c>
       <c r="K4" t="n">
-        <v>13.07324600795663</v>
+        <v>13.0434049948444</v>
       </c>
       <c r="L4" t="n">
-        <v>44.23988973062559</v>
+        <v>44.28353070159253</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8190633118176</v>
+        <v>99.81775865585499</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.72041142655638</v>
+        <v>85.80796045641891</v>
       </c>
       <c r="C5" t="n">
-        <v>42.14372035778388</v>
+        <v>42.19236026132069</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12295900750268</v>
+        <v>2.121588450319102</v>
       </c>
       <c r="E5" t="n">
-        <v>7.014876971144804</v>
+        <v>7.068086628817174</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745673092228357</v>
+        <v>0.7457784132518254</v>
       </c>
       <c r="G5" t="n">
-        <v>32.33462708082174</v>
+        <v>32.33187098094784</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30096224250441</v>
+        <v>34.30580700958397</v>
       </c>
       <c r="I5" t="n">
-        <v>4.54085620592716</v>
+        <v>4.5737138906751</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660456826427231</v>
+        <v>4.661115082823907</v>
       </c>
       <c r="K5" t="n">
-        <v>14.27958857344362</v>
+        <v>14.19203954358107</v>
       </c>
       <c r="L5" t="n">
-        <v>43.42559599323445</v>
+        <v>43.4634134593537</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84890492446195</v>
+        <v>99.84781326425546</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.3167456270975</v>
+        <v>84.29706649881874</v>
       </c>
       <c r="C6" t="n">
-        <v>41.44514482528412</v>
+        <v>41.39166855610729</v>
       </c>
       <c r="D6" t="n">
-        <v>2.054178889084782</v>
+        <v>2.047473516434984</v>
       </c>
       <c r="E6" t="n">
-        <v>7.41922671314178</v>
+        <v>7.457369091923445</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7467902642750109</v>
+        <v>0.7469041034299408</v>
       </c>
       <c r="G6" t="n">
-        <v>31.28704233153651</v>
+        <v>31.20239910823738</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35235215665049</v>
+        <v>34.35758875777728</v>
       </c>
       <c r="I6" t="n">
-        <v>3.789716120690099</v>
+        <v>3.81718127457858</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667439151718818</v>
+        <v>4.668150646437129</v>
       </c>
       <c r="K6" t="n">
-        <v>15.68325437290252</v>
+        <v>15.70293350118126</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74546590720427</v>
+        <v>42.77835033463712</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87386510539091</v>
+        <v>99.87295239192568</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.601762267897</v>
+        <v>82.73152301074899</v>
       </c>
       <c r="C7" t="n">
-        <v>40.31860430004457</v>
+        <v>40.41876639786967</v>
       </c>
       <c r="D7" t="n">
-        <v>1.970260894769654</v>
+        <v>1.971257013898321</v>
       </c>
       <c r="E7" t="n">
-        <v>7.643155124441422</v>
+        <v>7.710615496195374</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477432081927858</v>
+        <v>0.7478626011414224</v>
       </c>
       <c r="G7" t="n">
-        <v>30.00889374649051</v>
+        <v>30.04090045553504</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39618757686814</v>
+        <v>34.40167965250544</v>
       </c>
       <c r="I7" t="n">
-        <v>3.162126665929581</v>
+        <v>3.185066534339504</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673395051204911</v>
+        <v>4.67414125713389</v>
       </c>
       <c r="K7" t="n">
-        <v>17.39823773210299</v>
+        <v>17.26847698925102</v>
       </c>
       <c r="L7" t="n">
-        <v>42.17788807561106</v>
+        <v>42.20672379969655</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89473010775862</v>
+        <v>99.89396718681725</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.54607633663768</v>
+        <v>87.62639530813269</v>
       </c>
       <c r="C8" t="n">
-        <v>42.64311998496336</v>
+        <v>42.73717385080023</v>
       </c>
       <c r="D8" t="n">
-        <v>1.974504936490169</v>
+        <v>1.97548474432067</v>
       </c>
       <c r="E8" t="n">
-        <v>9.492558877272725</v>
+        <v>9.554637293032538</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493538849210437</v>
+        <v>0.7494665327689527</v>
       </c>
       <c r="G8" t="n">
-        <v>30.51855772572379</v>
+        <v>30.5492431663725</v>
       </c>
       <c r="H8" t="n">
-        <v>34.470278706368</v>
+        <v>34.47546050737183</v>
       </c>
       <c r="I8" t="n">
-        <v>5.657360425105438</v>
+        <v>5.637937234460246</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683461780756522</v>
+        <v>4.684165829805954</v>
       </c>
       <c r="K8" t="n">
-        <v>12.45392366336231</v>
+        <v>12.37360469186732</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71478300575171</v>
+        <v>44.70169240740687</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81182665407738</v>
+        <v>99.81247095007441</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.48388460448534</v>
+        <v>85.64560074773826</v>
       </c>
       <c r="C9" t="n">
-        <v>41.45852819574226</v>
+        <v>41.63108401421973</v>
       </c>
       <c r="D9" t="n">
-        <v>1.880981826072768</v>
+        <v>1.885941683258933</v>
       </c>
       <c r="E9" t="n">
-        <v>9.830132170749708</v>
+        <v>9.906034292031146</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507339932572802</v>
+        <v>0.7508394987831419</v>
       </c>
       <c r="G9" t="n">
-        <v>29.07303566537573</v>
+        <v>29.1645335379633</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53376368983488</v>
+        <v>34.53861694402453</v>
       </c>
       <c r="I9" t="n">
-        <v>4.723149801336984</v>
+        <v>4.706887924282583</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692087457857999</v>
+        <v>4.692746867394637</v>
       </c>
       <c r="K9" t="n">
-        <v>14.51611539551464</v>
+        <v>14.35439925226173</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86820750804572</v>
+        <v>43.85790736589465</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84285109930264</v>
+        <v>99.84339063237611</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.23794305721366</v>
+        <v>83.47328383867097</v>
       </c>
       <c r="C10" t="n">
-        <v>39.94493513614724</v>
+        <v>40.18876653689735</v>
       </c>
       <c r="D10" t="n">
-        <v>1.780204009662029</v>
+        <v>1.788713809425989</v>
       </c>
       <c r="E10" t="n">
-        <v>9.960489439704276</v>
+        <v>10.05009841506674</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519191588384412</v>
+        <v>0.752017407814136</v>
       </c>
       <c r="G10" t="n">
-        <v>27.51538263004293</v>
+        <v>27.66098461468704</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58828130656828</v>
+        <v>34.59280075945026</v>
       </c>
       <c r="I10" t="n">
-        <v>3.942171769657437</v>
+        <v>3.928560033388457</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699494742740256</v>
+        <v>4.700108798838349</v>
       </c>
       <c r="K10" t="n">
-        <v>16.76205694278636</v>
+        <v>16.52671616132903</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1618093154737</v>
+        <v>43.15377041498799</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86880139440728</v>
+        <v>99.86925311321437</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.87407473618485</v>
+        <v>81.08243435011318</v>
       </c>
       <c r="C11" t="n">
-        <v>38.19165077411574</v>
+        <v>38.40659809640673</v>
       </c>
       <c r="D11" t="n">
-        <v>1.675274484571625</v>
+        <v>1.682710993446618</v>
       </c>
       <c r="E11" t="n">
-        <v>9.921660346765654</v>
+        <v>10.00087783664355</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529386496327369</v>
+        <v>0.7530308918378995</v>
       </c>
       <c r="G11" t="n">
-        <v>25.89355950393993</v>
+        <v>26.02173844435652</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63517788310589</v>
+        <v>34.63942102454338</v>
       </c>
       <c r="I11" t="n">
-        <v>3.289597307964419</v>
+        <v>3.278212085298341</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705866560204604</v>
+        <v>4.706443073986871</v>
       </c>
       <c r="K11" t="n">
-        <v>19.12592526381515</v>
+        <v>18.91756564988682</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57291919068974</v>
+        <v>42.56670958611232</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89049522862062</v>
+        <v>99.89087333240587</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.47601251197781</v>
+        <v>78.70314400598379</v>
       </c>
       <c r="C12" t="n">
-        <v>36.30225927569796</v>
+        <v>36.53437505622439</v>
       </c>
       <c r="D12" t="n">
-        <v>1.569944370713758</v>
+        <v>1.578354366685532</v>
       </c>
       <c r="E12" t="n">
-        <v>9.755273491273984</v>
+        <v>9.836488403724189</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538163956919012</v>
+        <v>0.7539031761010047</v>
       </c>
       <c r="G12" t="n">
-        <v>24.26554475420604</v>
+        <v>24.4079492333226</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67555420182745</v>
+        <v>34.67954610064622</v>
       </c>
       <c r="I12" t="n">
-        <v>2.744526825190289</v>
+        <v>2.735007874872962</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71135247307438</v>
+        <v>4.711894850631278</v>
       </c>
       <c r="K12" t="n">
-        <v>21.5239874880222</v>
+        <v>21.29685599401622</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08237553328085</v>
+        <v>42.07770750294554</v>
       </c>
       <c r="M12" t="n">
-        <v>99.908622297001</v>
+        <v>99.90893855318615</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.10357927658352</v>
+        <v>76.20193235098002</v>
       </c>
       <c r="C13" t="n">
-        <v>34.35333005776784</v>
+        <v>34.45534572967304</v>
       </c>
       <c r="D13" t="n">
-        <v>1.466763284170473</v>
+        <v>1.469616021073089</v>
       </c>
       <c r="E13" t="n">
-        <v>9.495696450144402</v>
+        <v>9.539059659118026</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545722894318601</v>
+        <v>0.7546555589229768</v>
       </c>
       <c r="G13" t="n">
-        <v>22.67074603393967</v>
+        <v>22.72640035213097</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71032531386555</v>
+        <v>34.71415571045694</v>
       </c>
       <c r="I13" t="n">
-        <v>2.289399096082437</v>
+        <v>2.281447806009413</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716076808949124</v>
+        <v>4.716597243268604</v>
       </c>
       <c r="K13" t="n">
-        <v>23.89642072341647</v>
+        <v>23.79806764901998</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6740123625604</v>
+        <v>41.6706141803383</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92376314374471</v>
+        <v>99.92402755903133</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.14211564606674</v>
+        <v>83.09754430029395</v>
       </c>
       <c r="C14" t="n">
-        <v>38.74716360785943</v>
+        <v>38.81230215478321</v>
       </c>
       <c r="D14" t="n">
-        <v>1.468491634646016</v>
+        <v>1.471289168555865</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93407169731115</v>
+        <v>11.95018062251941</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554614345238768</v>
+        <v>0.7555147289583256</v>
       </c>
       <c r="G14" t="n">
-        <v>24.63479629638173</v>
+        <v>24.67950516722056</v>
       </c>
       <c r="H14" t="n">
-        <v>36.68856233213818</v>
+        <v>36.68090850053748</v>
       </c>
       <c r="I14" t="n">
-        <v>2.939098285291561</v>
+        <v>2.838179056512765</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721633965774229</v>
+        <v>4.721967055989534</v>
       </c>
       <c r="K14" t="n">
-        <v>16.85788435393325</v>
+        <v>16.90245569970606</v>
       </c>
       <c r="L14" t="n">
-        <v>44.29709740170534</v>
+        <v>44.19074376270314</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90214536349802</v>
+        <v>99.90550161719241</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.43723061189455</v>
+        <v>82.30271154145869</v>
       </c>
       <c r="C15" t="n">
-        <v>38.49614412386998</v>
+        <v>38.45584846404567</v>
       </c>
       <c r="D15" t="n">
-        <v>1.44270723125503</v>
+        <v>1.441977563685276</v>
       </c>
       <c r="E15" t="n">
-        <v>12.13314093315429</v>
+        <v>12.10667389289849</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562103465939373</v>
+        <v>0.7562391353855149</v>
       </c>
       <c r="G15" t="n">
-        <v>24.20224802019506</v>
+        <v>24.1878303018552</v>
       </c>
       <c r="H15" t="n">
-        <v>36.72493282824566</v>
+        <v>36.71607907346538</v>
       </c>
       <c r="I15" t="n">
-        <v>2.451676586238469</v>
+        <v>2.367416978009353</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726314666212107</v>
+        <v>4.726494596159467</v>
       </c>
       <c r="K15" t="n">
-        <v>17.56276938810542</v>
+        <v>17.69728845854132</v>
       </c>
       <c r="L15" t="n">
-        <v>43.85944486898872</v>
+        <v>43.76802477028765</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91835838096412</v>
+        <v>99.92116169287465</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.97441832102105</v>
+        <v>79.80481158763533</v>
       </c>
       <c r="C16" t="n">
-        <v>36.41200487730234</v>
+        <v>36.32362885361356</v>
       </c>
       <c r="D16" t="n">
-        <v>1.349804348626518</v>
+        <v>1.34763889354477</v>
       </c>
       <c r="E16" t="n">
-        <v>11.69263026685132</v>
+        <v>11.64369660753168</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568548454998407</v>
+        <v>0.7568628132755394</v>
       </c>
       <c r="G16" t="n">
-        <v>22.64374844491369</v>
+        <v>22.60538699501933</v>
       </c>
       <c r="H16" t="n">
-        <v>36.7562325573935</v>
+        <v>36.74635918679863</v>
       </c>
       <c r="I16" t="n">
-        <v>2.044805073362165</v>
+        <v>1.974474508493278</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730342784374004</v>
+        <v>4.730392582972121</v>
       </c>
       <c r="K16" t="n">
-        <v>20.02558167897897</v>
+        <v>20.19518841236465</v>
       </c>
       <c r="L16" t="n">
-        <v>43.49431131632316</v>
+        <v>43.41542115129931</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93189787260445</v>
+        <v>99.93423841727753</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.84958588856358</v>
+        <v>81.50934158670273</v>
       </c>
       <c r="C17" t="n">
-        <v>37.75957621412794</v>
+        <v>37.57198619107749</v>
       </c>
       <c r="D17" t="n">
-        <v>1.350930841001575</v>
+        <v>1.348713794777679</v>
       </c>
       <c r="E17" t="n">
-        <v>12.53197790859211</v>
+        <v>12.42520350575191</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574864860878627</v>
+        <v>0.7574665007878469</v>
       </c>
       <c r="G17" t="n">
-        <v>23.15069360080081</v>
+        <v>23.0705704876482</v>
       </c>
       <c r="H17" t="n">
-        <v>37.27495542444447</v>
+        <v>37.22282177541997</v>
       </c>
       <c r="I17" t="n">
-        <v>2.049251089587605</v>
+        <v>1.950399892393083</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734290538049142</v>
+        <v>4.734165629924043</v>
       </c>
       <c r="K17" t="n">
-        <v>18.15041411143644</v>
+        <v>18.49065841329725</v>
       </c>
       <c r="L17" t="n">
-        <v>44.02175826466195</v>
+        <v>43.87239388036204</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93174859022632</v>
+        <v>99.93503848473678</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.56018951216818</v>
+        <v>79.1607752761724</v>
       </c>
       <c r="C18" t="n">
-        <v>35.78631066697414</v>
+        <v>35.52427685237878</v>
       </c>
       <c r="D18" t="n">
-        <v>1.268324519077968</v>
+        <v>1.263607981572366</v>
       </c>
       <c r="E18" t="n">
-        <v>12.05049819857298</v>
+        <v>11.91222938801647</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580288397711992</v>
+        <v>0.7579852672471039</v>
       </c>
       <c r="G18" t="n">
-        <v>21.73508179425954</v>
+        <v>21.61478374470513</v>
       </c>
       <c r="H18" t="n">
-        <v>37.30164396574777</v>
+        <v>37.24831458788879</v>
       </c>
       <c r="I18" t="n">
-        <v>1.708931946168714</v>
+        <v>1.626446386448141</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737680248569995</v>
+        <v>4.737407920294399</v>
       </c>
       <c r="K18" t="n">
-        <v>20.43981048783183</v>
+        <v>20.8392247238276</v>
       </c>
       <c r="L18" t="n">
-        <v>43.71695520381662</v>
+        <v>43.58232064900492</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94307635862259</v>
+        <v>99.9458222252113</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.67051010762565</v>
+        <v>78.22566058787731</v>
       </c>
       <c r="C19" t="n">
-        <v>35.15960560632924</v>
+        <v>34.83730735581029</v>
       </c>
       <c r="D19" t="n">
-        <v>1.236880375839045</v>
+        <v>1.230268153398627</v>
       </c>
       <c r="E19" t="n">
-        <v>11.98923871597266</v>
+        <v>11.8242913222463</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758486515799363</v>
+        <v>0.7584239438281101</v>
       </c>
       <c r="G19" t="n">
-        <v>21.19622835811748</v>
+        <v>21.04448568821115</v>
       </c>
       <c r="H19" t="n">
-        <v>37.32416562634762</v>
+        <v>37.26987168668439</v>
       </c>
       <c r="I19" t="n">
-        <v>1.424969791803451</v>
+        <v>1.358170144583063</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740540723746019</v>
+        <v>4.740149648925687</v>
       </c>
       <c r="K19" t="n">
-        <v>21.32948989237437</v>
+        <v>21.77433941212269</v>
       </c>
       <c r="L19" t="n">
-        <v>43.46343416945836</v>
+        <v>43.34310707968368</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95252966816196</v>
+        <v>99.95475384761664</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.04975424609283</v>
+        <v>75.68091163360732</v>
       </c>
       <c r="C20" t="n">
-        <v>32.7579905752796</v>
+        <v>32.5013548957174</v>
       </c>
       <c r="D20" t="n">
-        <v>1.143305182603073</v>
+        <v>1.139023309724511</v>
       </c>
       <c r="E20" t="n">
-        <v>11.28021800711927</v>
+        <v>11.13605229927946</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588814996210427</v>
+        <v>0.7588022068687159</v>
       </c>
       <c r="G20" t="n">
-        <v>19.59264469454843</v>
+        <v>19.48368709197145</v>
       </c>
       <c r="H20" t="n">
-        <v>37.34360228246874</v>
+        <v>37.28845999089329</v>
       </c>
       <c r="I20" t="n">
-        <v>1.188093207100751</v>
+        <v>1.13237294194042</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743009372631517</v>
+        <v>4.742513792929474</v>
       </c>
       <c r="K20" t="n">
-        <v>23.95024575390715</v>
+        <v>24.31908836639267</v>
       </c>
       <c r="L20" t="n">
-        <v>43.25218117659652</v>
+        <v>43.14182978942929</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96041750578328</v>
+        <v>99.96227305153937</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.95982633827342</v>
+        <v>81.48404194836429</v>
       </c>
       <c r="C21" t="n">
-        <v>36.44425749790652</v>
+        <v>36.1609944820766</v>
       </c>
       <c r="D21" t="n">
-        <v>1.14408608603703</v>
+        <v>1.139744938099487</v>
       </c>
       <c r="E21" t="n">
-        <v>13.26373084785415</v>
+        <v>13.09503704655816</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593998329392486</v>
+        <v>0.7592829461115355</v>
       </c>
       <c r="G21" t="n">
-        <v>21.30193298754548</v>
+        <v>21.18983935434904</v>
       </c>
       <c r="H21" t="n">
-        <v>39.06501488308494</v>
+        <v>39.00589246959671</v>
       </c>
       <c r="I21" t="n">
-        <v>1.679412744942276</v>
+        <v>1.548726780452271</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746248955870304</v>
+        <v>4.745518413197096</v>
       </c>
       <c r="K21" t="n">
-        <v>18.04017366172656</v>
+        <v>18.5159580516357</v>
       </c>
       <c r="L21" t="n">
-        <v>45.45962662534025</v>
+        <v>45.27145592610002</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94405778497332</v>
+        <v>99.94840845981231</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_61_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_61_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.33367885473822</v>
+        <v>46.03927068131314</v>
       </c>
       <c r="M2" t="n">
-        <v>98.97227603234384</v>
+        <v>99.05852767657598</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00213157996774</v>
+        <v>88.08032778461103</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90164001475909</v>
+        <v>45.95670624349029</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228686528836853</v>
+        <v>2.228845304681737</v>
       </c>
       <c r="E3" t="n">
-        <v>5.689582473511602</v>
+        <v>5.725235481381423</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428955096122843</v>
+        <v>0.7429484348939124</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96398830154435</v>
+        <v>33.98229949964343</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17319344216508</v>
+        <v>34.17562800511997</v>
       </c>
       <c r="I3" t="n">
-        <v>6.560688389220801</v>
+        <v>6.581943340803591</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643096935076777</v>
+        <v>4.643427718086953</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99786842003226</v>
+        <v>11.91967221538901</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86499183729869</v>
+        <v>48.88737568495551</v>
       </c>
       <c r="M3" t="n">
-        <v>106.76450027209</v>
+        <v>106.7637541438348</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.95659500515561</v>
+        <v>87.09261914896791</v>
       </c>
       <c r="C4" t="n">
-        <v>42.49082295941807</v>
+        <v>42.60577888229125</v>
       </c>
       <c r="D4" t="n">
-        <v>2.17761402821628</v>
+        <v>2.180928696416743</v>
       </c>
       <c r="E4" t="n">
-        <v>6.472320619925712</v>
+        <v>6.518233987372578</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444557203256932</v>
+        <v>0.7445113724366766</v>
       </c>
       <c r="G4" t="n">
-        <v>33.18567076286697</v>
+        <v>33.25173442648747</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24496313498189</v>
+        <v>34.24752313208712</v>
       </c>
       <c r="I4" t="n">
-        <v>5.478722486803479</v>
+        <v>5.496491456438089</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652848252035581</v>
+        <v>4.65319607772923</v>
       </c>
       <c r="K4" t="n">
-        <v>13.0434049948444</v>
+        <v>12.90738085103209</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28353070159253</v>
+        <v>44.30400850720991</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81775865585499</v>
+        <v>99.81716824053325</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.80796045641891</v>
+        <v>85.91701817141535</v>
       </c>
       <c r="C5" t="n">
-        <v>42.19236026132069</v>
+        <v>42.28320909633287</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121588450319102</v>
+        <v>2.123585714927944</v>
       </c>
       <c r="E5" t="n">
-        <v>7.068086628817174</v>
+        <v>7.111611211550438</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457784132518254</v>
+        <v>0.7458367745340769</v>
       </c>
       <c r="G5" t="n">
-        <v>32.33187098094784</v>
+        <v>32.37744926768273</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30580700958397</v>
+        <v>34.30849162856754</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5737138906751</v>
+        <v>4.588563733314643</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661115082823907</v>
+        <v>4.661479840837981</v>
       </c>
       <c r="K5" t="n">
-        <v>14.19203954358107</v>
+        <v>14.08298182858465</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4634134593537</v>
+        <v>43.48112875684809</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84781326425546</v>
+        <v>99.84731968176561</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.29706649881874</v>
+        <v>84.58739677370951</v>
       </c>
       <c r="C6" t="n">
-        <v>41.39166855610729</v>
+        <v>41.66616208950529</v>
       </c>
       <c r="D6" t="n">
-        <v>2.047473516434984</v>
+        <v>2.058834527961823</v>
       </c>
       <c r="E6" t="n">
-        <v>7.457369091923445</v>
+        <v>7.533030224034574</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469041034299408</v>
+        <v>0.7469623310568007</v>
       </c>
       <c r="G6" t="n">
-        <v>31.20239910823738</v>
+        <v>31.3902142075293</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35758875777728</v>
+        <v>34.36026722861283</v>
       </c>
       <c r="I6" t="n">
-        <v>3.81718127457858</v>
+        <v>3.829573685409189</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668150646437129</v>
+        <v>4.668514569105005</v>
       </c>
       <c r="K6" t="n">
-        <v>15.70293350118126</v>
+        <v>15.41260322629046</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77835033463712</v>
+        <v>42.79377458050106</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87295239192568</v>
+        <v>99.87253989629681</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.73152301074899</v>
+        <v>83.12665630734556</v>
       </c>
       <c r="C7" t="n">
-        <v>40.41876639786967</v>
+        <v>40.80018605830313</v>
       </c>
       <c r="D7" t="n">
-        <v>1.971257013898321</v>
+        <v>1.987994707320769</v>
       </c>
       <c r="E7" t="n">
-        <v>7.710615496195374</v>
+        <v>7.806402519898365</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478626011414224</v>
+        <v>0.7479194423501988</v>
       </c>
       <c r="G7" t="n">
-        <v>30.04090045553504</v>
+        <v>30.3101482215819</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40167965250544</v>
+        <v>34.40429434810915</v>
       </c>
       <c r="I7" t="n">
-        <v>3.185066534339504</v>
+        <v>3.195400553396442</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67414125713389</v>
+        <v>4.674496514688744</v>
       </c>
       <c r="K7" t="n">
-        <v>17.26847698925102</v>
+        <v>16.87334369265445</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20672379969655</v>
+        <v>42.2200932022255</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89396718681725</v>
+        <v>99.89362295318307</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.62639530813269</v>
+        <v>88.00658648752236</v>
       </c>
       <c r="C8" t="n">
-        <v>42.73717385080023</v>
+        <v>43.03710588607418</v>
       </c>
       <c r="D8" t="n">
-        <v>1.97548474432067</v>
+        <v>1.992296438205184</v>
       </c>
       <c r="E8" t="n">
-        <v>9.554637293032538</v>
+        <v>9.600262314152577</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494665327689527</v>
+        <v>0.7495378310472935</v>
       </c>
       <c r="G8" t="n">
-        <v>30.5492431663725</v>
+        <v>30.78813532905351</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47546050737183</v>
+        <v>34.4787402281755</v>
       </c>
       <c r="I8" t="n">
-        <v>5.637937234460246</v>
+        <v>5.713002902842701</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684165829805954</v>
+        <v>4.684611444045586</v>
       </c>
       <c r="K8" t="n">
-        <v>12.37360469186732</v>
+        <v>11.99341351247765</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70169240740687</v>
+        <v>44.7794583518143</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81247095007441</v>
+        <v>99.80997775036613</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.64560074773826</v>
+        <v>86.1610872562499</v>
       </c>
       <c r="C9" t="n">
-        <v>41.63108401421973</v>
+        <v>42.07820530658094</v>
       </c>
       <c r="D9" t="n">
-        <v>1.885941683258933</v>
+        <v>1.909056557451111</v>
       </c>
       <c r="E9" t="n">
-        <v>9.906034292031146</v>
+        <v>9.994091759441929</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508394987831419</v>
+        <v>0.7509209036148043</v>
       </c>
       <c r="G9" t="n">
-        <v>29.1645335379633</v>
+        <v>29.50178021427981</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53861694402453</v>
+        <v>34.542361566281</v>
       </c>
       <c r="I9" t="n">
-        <v>4.706887924282583</v>
+        <v>4.769620607588735</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692746867394637</v>
+        <v>4.693255647592529</v>
       </c>
       <c r="K9" t="n">
-        <v>14.35439925226173</v>
+        <v>13.83891274375009</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85790736589465</v>
+        <v>43.92418742459001</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84339063237611</v>
+        <v>99.84130547492103</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.47328383867097</v>
+        <v>84.16607599361167</v>
       </c>
       <c r="C10" t="n">
-        <v>40.18876653689735</v>
+        <v>40.82328547875895</v>
       </c>
       <c r="D10" t="n">
-        <v>1.788713809425989</v>
+        <v>1.81993743865933</v>
       </c>
       <c r="E10" t="n">
-        <v>10.05009841506674</v>
+        <v>10.19103647561374</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752017407814136</v>
+        <v>0.7521048243555556</v>
       </c>
       <c r="G10" t="n">
-        <v>27.66098461468704</v>
+        <v>28.124569756463</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59280075945026</v>
+        <v>34.59682192035555</v>
       </c>
       <c r="I10" t="n">
-        <v>3.928560033388457</v>
+        <v>3.980950425942261</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700108798838349</v>
+        <v>4.700655152222224</v>
       </c>
       <c r="K10" t="n">
-        <v>16.52671616132903</v>
+        <v>15.83392400638834</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15377041498799</v>
+        <v>43.21030105353081</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86925311321437</v>
+        <v>99.86751053867809</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.08243435011318</v>
+        <v>81.88748707233745</v>
       </c>
       <c r="C11" t="n">
-        <v>38.40659809640673</v>
+        <v>39.16196935519831</v>
       </c>
       <c r="D11" t="n">
-        <v>1.682710993446618</v>
+        <v>1.718936597942321</v>
       </c>
       <c r="E11" t="n">
-        <v>10.00087783664355</v>
+        <v>10.17912324501443</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530308918378995</v>
+        <v>0.753121850161117</v>
       </c>
       <c r="G11" t="n">
-        <v>26.02173844435652</v>
+        <v>26.56374402154132</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63942102454338</v>
+        <v>34.64360510741137</v>
       </c>
       <c r="I11" t="n">
-        <v>3.278212085298341</v>
+        <v>3.321944686759913</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706443073986871</v>
+        <v>4.707011563506982</v>
       </c>
       <c r="K11" t="n">
-        <v>18.91756564988682</v>
+        <v>18.11251292766253</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56670958611232</v>
+        <v>42.614935760863</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89087333240587</v>
+        <v>99.88941804372384</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.70314400598379</v>
+        <v>79.64249073316967</v>
       </c>
       <c r="C12" t="n">
-        <v>36.53437505622439</v>
+        <v>37.43131058198584</v>
       </c>
       <c r="D12" t="n">
-        <v>1.578354366685532</v>
+        <v>1.620480663458365</v>
       </c>
       <c r="E12" t="n">
-        <v>9.836488403724189</v>
+        <v>10.05800761370817</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539031761010047</v>
+        <v>0.7539954525016869</v>
       </c>
       <c r="G12" t="n">
-        <v>24.4079492333226</v>
+        <v>25.04224622798442</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67954610064622</v>
+        <v>34.68379081507759</v>
       </c>
       <c r="I12" t="n">
-        <v>2.735007874872962</v>
+        <v>2.771498382303908</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711894850631278</v>
+        <v>4.712471578135544</v>
       </c>
       <c r="K12" t="n">
-        <v>21.29685599401622</v>
+        <v>20.35750926683032</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07770750294554</v>
+        <v>42.11890390988495</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90893855318615</v>
+        <v>99.90772375870111</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.20193235098002</v>
+        <v>77.34162964625781</v>
       </c>
       <c r="C13" t="n">
-        <v>34.45534572967304</v>
+        <v>35.55879920161631</v>
       </c>
       <c r="D13" t="n">
-        <v>1.469616021073089</v>
+        <v>1.520457466382696</v>
       </c>
       <c r="E13" t="n">
-        <v>9.539059659118026</v>
+        <v>9.822496999340213</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546555589229768</v>
+        <v>0.7547467294261947</v>
       </c>
       <c r="G13" t="n">
-        <v>22.72640035213097</v>
+        <v>23.49652859854139</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71415571045694</v>
+        <v>34.71834955360494</v>
       </c>
       <c r="I13" t="n">
-        <v>2.281447806009413</v>
+        <v>2.311883240048657</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716597243268604</v>
+        <v>4.717167058913717</v>
       </c>
       <c r="K13" t="n">
-        <v>23.79806764901998</v>
+        <v>22.65837035374219</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6706141803383</v>
+        <v>41.70584437846639</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92402755903133</v>
+        <v>99.92301393382488</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.09754430029395</v>
+        <v>83.87800427273902</v>
       </c>
       <c r="C14" t="n">
-        <v>38.81230215478321</v>
+        <v>39.58881916701641</v>
       </c>
       <c r="D14" t="n">
-        <v>1.471289168555865</v>
+        <v>1.522276394792464</v>
       </c>
       <c r="E14" t="n">
-        <v>11.95018062251941</v>
+        <v>12.08479059331865</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555147289583256</v>
+        <v>0.7556496354914325</v>
       </c>
       <c r="G14" t="n">
-        <v>24.67950516722056</v>
+        <v>25.27346278168701</v>
       </c>
       <c r="H14" t="n">
-        <v>36.68090850053748</v>
+        <v>36.50870843911535</v>
       </c>
       <c r="I14" t="n">
-        <v>2.838179056512765</v>
+        <v>3.01030620651267</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721967055989534</v>
+        <v>4.722810221821454</v>
       </c>
       <c r="K14" t="n">
-        <v>16.90245569970606</v>
+        <v>16.12199572726097</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19074376270314</v>
+        <v>44.18896146338784</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90550161719241</v>
+        <v>99.89977635766522</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.30271154145869</v>
+        <v>83.26409779831938</v>
       </c>
       <c r="C15" t="n">
-        <v>38.45584846404567</v>
+        <v>39.44037101510781</v>
       </c>
       <c r="D15" t="n">
-        <v>1.441977563685276</v>
+        <v>1.499746469714273</v>
       </c>
       <c r="E15" t="n">
-        <v>12.10667389289849</v>
+        <v>12.32445222104976</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562391353855149</v>
+        <v>0.7564092744640883</v>
       </c>
       <c r="G15" t="n">
-        <v>24.1878303018552</v>
+        <v>24.89941164032677</v>
       </c>
       <c r="H15" t="n">
-        <v>36.71607907346538</v>
+        <v>36.54540988972035</v>
       </c>
       <c r="I15" t="n">
-        <v>2.367416978009353</v>
+        <v>2.511110337643606</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726494596159467</v>
+        <v>4.727557965400553</v>
       </c>
       <c r="K15" t="n">
-        <v>17.69728845854132</v>
+        <v>16.73590220168059</v>
       </c>
       <c r="L15" t="n">
-        <v>43.76802477028765</v>
+        <v>43.74010716636403</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92116169287465</v>
+        <v>99.91638038315243</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.80481158763533</v>
+        <v>80.9931386438098</v>
       </c>
       <c r="C16" t="n">
-        <v>36.32362885361356</v>
+        <v>37.55782577571797</v>
       </c>
       <c r="D16" t="n">
-        <v>1.34763889354477</v>
+        <v>1.413010248856844</v>
       </c>
       <c r="E16" t="n">
-        <v>11.64369660753168</v>
+        <v>11.96074675634103</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568628132755394</v>
+        <v>0.7570612722130873</v>
       </c>
       <c r="G16" t="n">
-        <v>22.60538699501933</v>
+        <v>23.45938100123691</v>
       </c>
       <c r="H16" t="n">
-        <v>36.74635918679863</v>
+        <v>36.57691072635568</v>
       </c>
       <c r="I16" t="n">
-        <v>1.974474508493278</v>
+        <v>2.094395687474436</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730392582972121</v>
+        <v>4.731632951331797</v>
       </c>
       <c r="K16" t="n">
-        <v>20.19518841236465</v>
+        <v>19.00686135619023</v>
       </c>
       <c r="L16" t="n">
-        <v>43.41542115129931</v>
+        <v>43.36555980315724</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93423841727753</v>
+        <v>99.93024693506544</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.50934158670273</v>
+        <v>82.72993868991577</v>
       </c>
       <c r="C17" t="n">
-        <v>37.57198619107749</v>
+        <v>38.82589319754166</v>
       </c>
       <c r="D17" t="n">
-        <v>1.348713794777679</v>
+        <v>1.414196434532794</v>
       </c>
       <c r="E17" t="n">
-        <v>12.42520350575191</v>
+        <v>12.76277724772996</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574665007878469</v>
+        <v>0.7576968056337698</v>
       </c>
       <c r="G17" t="n">
-        <v>23.0705704876482</v>
+        <v>23.92381604603753</v>
       </c>
       <c r="H17" t="n">
-        <v>37.22282177541997</v>
+        <v>37.05235759918541</v>
       </c>
       <c r="I17" t="n">
-        <v>1.950399892393083</v>
+        <v>2.083489521585248</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734165629924043</v>
+        <v>4.735605035211062</v>
       </c>
       <c r="K17" t="n">
-        <v>18.49065841329725</v>
+        <v>17.27006131008424</v>
       </c>
       <c r="L17" t="n">
-        <v>43.87239388036204</v>
+        <v>43.83465409394465</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93503848473678</v>
+        <v>99.93060860157055</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.1607752761724</v>
+        <v>80.54471556241799</v>
       </c>
       <c r="C18" t="n">
-        <v>35.52427685237878</v>
+        <v>36.9626369511009</v>
       </c>
       <c r="D18" t="n">
-        <v>1.263607981572366</v>
+        <v>1.334045534195381</v>
       </c>
       <c r="E18" t="n">
-        <v>11.91222938801647</v>
+        <v>12.32901657894365</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579852672471039</v>
+        <v>0.7582416336034162</v>
       </c>
       <c r="G18" t="n">
-        <v>21.61478374470513</v>
+        <v>22.56791148513397</v>
       </c>
       <c r="H18" t="n">
-        <v>37.24831458788879</v>
+        <v>37.07900039431306</v>
       </c>
       <c r="I18" t="n">
-        <v>1.626446386448141</v>
+        <v>1.737489726207169</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737407920294399</v>
+        <v>4.739010210021353</v>
       </c>
       <c r="K18" t="n">
-        <v>20.8392247238276</v>
+        <v>19.455284437582</v>
       </c>
       <c r="L18" t="n">
-        <v>43.58232064900492</v>
+        <v>43.52420390238417</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9458222252113</v>
+        <v>99.94212529106707</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.22566058787731</v>
+        <v>79.73839635544306</v>
       </c>
       <c r="C19" t="n">
-        <v>34.83730735581029</v>
+        <v>36.42421404243024</v>
       </c>
       <c r="D19" t="n">
-        <v>1.230268153398627</v>
+        <v>1.305146363294927</v>
       </c>
       <c r="E19" t="n">
-        <v>11.8242913222463</v>
+        <v>12.30339964221664</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584239438281101</v>
+        <v>0.7587008557467614</v>
       </c>
       <c r="G19" t="n">
-        <v>21.04448568821115</v>
+        <v>22.07902717484798</v>
       </c>
       <c r="H19" t="n">
-        <v>37.26987168668439</v>
+        <v>37.10145695338282</v>
       </c>
       <c r="I19" t="n">
-        <v>1.358170144583063</v>
+        <v>1.448785017536665</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740149648925687</v>
+        <v>4.74188034841726</v>
       </c>
       <c r="K19" t="n">
-        <v>21.77433941212269</v>
+        <v>20.26160364455695</v>
       </c>
       <c r="L19" t="n">
-        <v>43.34310707968368</v>
+        <v>43.26591870950705</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95475384761664</v>
+        <v>99.95173639649423</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.68091163360732</v>
+        <v>77.2722559398521</v>
       </c>
       <c r="C20" t="n">
-        <v>32.5013548957174</v>
+        <v>34.18135376183991</v>
       </c>
       <c r="D20" t="n">
-        <v>1.139023309724511</v>
+        <v>1.215589116732603</v>
       </c>
       <c r="E20" t="n">
-        <v>11.13605229927946</v>
+        <v>11.6604832334501</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588022068687159</v>
+        <v>0.7590961993086799</v>
       </c>
       <c r="G20" t="n">
-        <v>19.48368709197145</v>
+        <v>20.56399641955232</v>
       </c>
       <c r="H20" t="n">
-        <v>37.28845999089329</v>
+        <v>37.12078976688002</v>
       </c>
       <c r="I20" t="n">
-        <v>1.13237294194042</v>
+        <v>1.207949958249114</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742513792929474</v>
+        <v>4.744351245679251</v>
       </c>
       <c r="K20" t="n">
-        <v>24.31908836639267</v>
+        <v>22.72774406014789</v>
       </c>
       <c r="L20" t="n">
-        <v>43.14182978942929</v>
+        <v>43.05065814974731</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96227305153937</v>
+        <v>99.95975597173512</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.48404194836429</v>
+        <v>82.75157640931737</v>
       </c>
       <c r="C21" t="n">
-        <v>36.1609944820766</v>
+        <v>37.53876546133581</v>
       </c>
       <c r="D21" t="n">
-        <v>1.139744938099487</v>
+        <v>1.216454548792373</v>
       </c>
       <c r="E21" t="n">
-        <v>13.09503704655816</v>
+        <v>13.48706023920883</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592829461115355</v>
+        <v>0.7596366337188669</v>
       </c>
       <c r="G21" t="n">
-        <v>21.18983935434904</v>
+        <v>22.10233955950336</v>
       </c>
       <c r="H21" t="n">
-        <v>39.00589246959671</v>
+        <v>38.67092042579823</v>
       </c>
       <c r="I21" t="n">
-        <v>1.548726780452271</v>
+        <v>1.767436041552783</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745518413197096</v>
+        <v>4.74772896074292</v>
       </c>
       <c r="K21" t="n">
-        <v>18.5159580516357</v>
+        <v>17.24842359068264</v>
       </c>
       <c r="L21" t="n">
-        <v>45.27145592610002</v>
+        <v>45.15393832730517</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94840845981231</v>
+        <v>99.94112737932362</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_61_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_61_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>46.03927068131314</v>
+        <v>43.56880002794924</v>
       </c>
       <c r="M2" t="n">
-        <v>99.05852767657598</v>
+        <v>96.24386395688421</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08032778461103</v>
+        <v>81.58454896455059</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95670624349029</v>
+        <v>43.34010452010615</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228845304681737</v>
+        <v>2.185236830459873</v>
       </c>
       <c r="E3" t="n">
-        <v>5.725235481381423</v>
+        <v>4.172924305997398</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429484348939124</v>
+        <v>0.7377088621757806</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98229949964343</v>
+        <v>32.86960399150059</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17562800511997</v>
+        <v>33.9346076600859</v>
       </c>
       <c r="I3" t="n">
-        <v>6.581943340803591</v>
+        <v>3.073786925732419</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643427718086953</v>
+        <v>4.610680388598628</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91967221538901</v>
+        <v>18.4154510354494</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88737568495551</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637541438348</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.09261914896791</v>
+        <v>88.74281180488241</v>
       </c>
       <c r="C4" t="n">
-        <v>42.60577888229125</v>
+        <v>42.92039672965899</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180928696416743</v>
+        <v>2.191032637575217</v>
       </c>
       <c r="E4" t="n">
-        <v>6.518233987372578</v>
+        <v>6.551446335265746</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445113724366766</v>
+        <v>0.7396654548035696</v>
       </c>
       <c r="G4" t="n">
-        <v>33.25173442648747</v>
+        <v>33.55208817430606</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24752313208712</v>
+        <v>34.0246109209642</v>
       </c>
       <c r="I4" t="n">
-        <v>5.496491456438089</v>
+        <v>7.061059189445309</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65319607772923</v>
+        <v>4.62290909252231</v>
       </c>
       <c r="K4" t="n">
-        <v>12.90738085103209</v>
+        <v>11.25718819511756</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30400850720991</v>
+        <v>45.58766904210929</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81716824053325</v>
+        <v>99.76525396688585</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.91701817141535</v>
+        <v>87.78835546285408</v>
       </c>
       <c r="C5" t="n">
-        <v>42.28320909633287</v>
+        <v>43.06047892512298</v>
       </c>
       <c r="D5" t="n">
-        <v>2.123585714927944</v>
+        <v>2.14638341355022</v>
       </c>
       <c r="E5" t="n">
-        <v>7.111611211550438</v>
+        <v>7.400838582504519</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458367745340769</v>
+        <v>0.7413217478507637</v>
       </c>
       <c r="G5" t="n">
-        <v>32.37744926768273</v>
+        <v>32.86835819433693</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30849162856754</v>
+        <v>34.10080040113512</v>
       </c>
       <c r="I5" t="n">
-        <v>4.588563733314643</v>
+        <v>5.897392199409265</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661479840837981</v>
+        <v>4.633260924067272</v>
       </c>
       <c r="K5" t="n">
-        <v>14.08298182858465</v>
+        <v>12.21164453714591</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48112875684809</v>
+        <v>44.53173600469093</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84731968176561</v>
+        <v>99.80385946695982</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.58739677370951</v>
+        <v>86.60353126781173</v>
       </c>
       <c r="C6" t="n">
-        <v>41.66616208950529</v>
+        <v>42.79115999311803</v>
       </c>
       <c r="D6" t="n">
-        <v>2.058834527961823</v>
+        <v>2.090381075500146</v>
       </c>
       <c r="E6" t="n">
-        <v>7.533030224034574</v>
+        <v>8.028374223858245</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469623310568007</v>
+        <v>0.742726665686095</v>
       </c>
       <c r="G6" t="n">
-        <v>31.3902142075293</v>
+        <v>32.01077380604464</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36026722861283</v>
+        <v>34.16542662156037</v>
       </c>
       <c r="I6" t="n">
-        <v>3.829573685409189</v>
+        <v>4.923807214624127</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668514569105005</v>
+        <v>4.642041660538093</v>
       </c>
       <c r="K6" t="n">
-        <v>15.41260322629046</v>
+        <v>13.39646873218827</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79377458050106</v>
+        <v>43.64855482471012</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87253989629681</v>
+        <v>99.83618355001641</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.12665630734556</v>
+        <v>85.20279401067113</v>
       </c>
       <c r="C7" t="n">
-        <v>40.80018605830313</v>
+        <v>42.15538062709074</v>
       </c>
       <c r="D7" t="n">
-        <v>1.987994707320769</v>
+        <v>2.024128605024691</v>
       </c>
       <c r="E7" t="n">
-        <v>7.806402519898365</v>
+        <v>8.458884842763245</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479194423501988</v>
+        <v>0.7439208501973751</v>
       </c>
       <c r="G7" t="n">
-        <v>30.3101482215819</v>
+        <v>30.99622537210705</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40429434810915</v>
+        <v>34.22035910907925</v>
       </c>
       <c r="I7" t="n">
-        <v>3.195400553396442</v>
+        <v>4.109769917765911</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674496514688744</v>
+        <v>4.649505313733593</v>
       </c>
       <c r="K7" t="n">
-        <v>16.87334369265445</v>
+        <v>14.79720598932889</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2200932022255</v>
+        <v>42.9106409609519</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89362295318307</v>
+        <v>99.86322757737153</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.00658648752236</v>
+        <v>83.68899460213824</v>
       </c>
       <c r="C8" t="n">
-        <v>43.03710588607418</v>
+        <v>41.28016163902698</v>
       </c>
       <c r="D8" t="n">
-        <v>1.992296438205184</v>
+        <v>1.952921302421329</v>
       </c>
       <c r="E8" t="n">
-        <v>9.600262314152577</v>
+        <v>8.732888788901187</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495378310472935</v>
+        <v>0.7449370198360962</v>
       </c>
       <c r="G8" t="n">
-        <v>30.78813532905351</v>
+        <v>29.90580177246294</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4787402281755</v>
+        <v>34.26710291246042</v>
       </c>
       <c r="I8" t="n">
-        <v>5.713002902842701</v>
+        <v>3.429486432080669</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684611444045586</v>
+        <v>4.655856373975601</v>
       </c>
       <c r="K8" t="n">
-        <v>11.99341351247765</v>
+        <v>16.31100539786176</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7794583518143</v>
+        <v>42.29467268761777</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80997775036613</v>
+        <v>99.88583972450651</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.1610872562499</v>
+        <v>82.06113646087287</v>
       </c>
       <c r="C9" t="n">
-        <v>42.07820530658094</v>
+        <v>40.18500830236738</v>
       </c>
       <c r="D9" t="n">
-        <v>1.909056557451111</v>
+        <v>1.876781413634421</v>
       </c>
       <c r="E9" t="n">
-        <v>9.994091759441929</v>
+        <v>8.869284787311905</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7509209036148043</v>
+        <v>0.7458028108559067</v>
       </c>
       <c r="G9" t="n">
-        <v>29.50178021427981</v>
+        <v>28.73984366743563</v>
       </c>
       <c r="H9" t="n">
-        <v>34.542361566281</v>
+        <v>34.30692929937171</v>
       </c>
       <c r="I9" t="n">
-        <v>4.769620607588735</v>
+        <v>2.861226914413871</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693255647592529</v>
+        <v>4.661267567849417</v>
       </c>
       <c r="K9" t="n">
-        <v>13.83891274375009</v>
+        <v>17.93886353912713</v>
       </c>
       <c r="L9" t="n">
-        <v>43.92418742459001</v>
+        <v>41.78086464650325</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84130547492103</v>
+        <v>99.90473648799775</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.16607599361167</v>
+        <v>86.55576040598037</v>
       </c>
       <c r="C10" t="n">
-        <v>40.82328547875895</v>
+        <v>43.33291453800938</v>
       </c>
       <c r="D10" t="n">
-        <v>1.81993743865933</v>
+        <v>1.87884092210598</v>
       </c>
       <c r="E10" t="n">
-        <v>10.19103647561374</v>
+        <v>10.66877759300163</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7521048243555556</v>
+        <v>0.7466212264667558</v>
       </c>
       <c r="G10" t="n">
-        <v>28.124569756463</v>
+        <v>30.08622668710273</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59682192035555</v>
+        <v>35.65942142686435</v>
       </c>
       <c r="I10" t="n">
-        <v>3.980950425942261</v>
+        <v>2.849489885021718</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700655152222224</v>
+        <v>4.666382665417223</v>
       </c>
       <c r="K10" t="n">
-        <v>15.83392400638834</v>
+        <v>13.44423959401963</v>
       </c>
       <c r="L10" t="n">
-        <v>43.21030105353081</v>
+        <v>43.127966988274</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86751053867809</v>
+        <v>99.90512112030299</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.88748707233745</v>
+        <v>86.43555521707241</v>
       </c>
       <c r="C11" t="n">
-        <v>39.16196935519831</v>
+        <v>43.54180365068778</v>
       </c>
       <c r="D11" t="n">
-        <v>1.718936597942321</v>
+        <v>1.865304446034899</v>
       </c>
       <c r="E11" t="n">
-        <v>10.17912324501443</v>
+        <v>11.04943730686242</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753121850161117</v>
+        <v>0.747323167288087</v>
       </c>
       <c r="G11" t="n">
-        <v>26.56374402154132</v>
+        <v>29.92067484152274</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64360510741137</v>
+        <v>35.74415711055249</v>
       </c>
       <c r="I11" t="n">
-        <v>3.321944686759913</v>
+        <v>2.43788854926121</v>
       </c>
       <c r="J11" t="n">
-        <v>4.707011563506982</v>
+        <v>4.670769795550544</v>
       </c>
       <c r="K11" t="n">
-        <v>18.11251292766253</v>
+        <v>13.56444478292761</v>
       </c>
       <c r="L11" t="n">
-        <v>42.614935760863</v>
+        <v>42.8125649428768</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88941804372384</v>
+        <v>99.91881337649218</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.64249073316967</v>
+        <v>84.74898138351567</v>
       </c>
       <c r="C12" t="n">
-        <v>37.43131058198584</v>
+        <v>42.23476155999326</v>
       </c>
       <c r="D12" t="n">
-        <v>1.620480663458365</v>
+        <v>1.793294103173539</v>
       </c>
       <c r="E12" t="n">
-        <v>10.05800761370817</v>
+        <v>10.96173861635878</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539954525016869</v>
+        <v>0.7479207973972121</v>
       </c>
       <c r="G12" t="n">
-        <v>25.04224622798442</v>
+        <v>28.76558294295285</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68379081507759</v>
+        <v>35.77274151078203</v>
       </c>
       <c r="I12" t="n">
-        <v>2.771498382303908</v>
+        <v>2.033198429118697</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712471578135544</v>
+        <v>4.674504983732575</v>
       </c>
       <c r="K12" t="n">
-        <v>20.35750926683032</v>
+        <v>15.25101861648433</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11890390988495</v>
+        <v>42.44650069715404</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90772375870111</v>
+        <v>99.93228087363163</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.34162964625781</v>
+        <v>85.8952405505631</v>
       </c>
       <c r="C13" t="n">
-        <v>35.55879920161631</v>
+        <v>43.2055155025846</v>
       </c>
       <c r="D13" t="n">
-        <v>1.520457466382696</v>
+        <v>1.794594582110008</v>
       </c>
       <c r="E13" t="n">
-        <v>9.822496999340213</v>
+        <v>11.59424314679802</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547467294261947</v>
+        <v>0.7484631820743498</v>
       </c>
       <c r="G13" t="n">
-        <v>23.49652859854139</v>
+        <v>29.09954679904717</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71834955360494</v>
+        <v>36.11178688814262</v>
       </c>
       <c r="I13" t="n">
-        <v>2.311883240048657</v>
+        <v>1.868711064426255</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717167058913717</v>
+        <v>4.677894887964686</v>
       </c>
       <c r="K13" t="n">
-        <v>22.65837035374219</v>
+        <v>14.10475944943688</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70584437846639</v>
+        <v>42.62747981878158</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92301393382488</v>
+        <v>99.93775477080307</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.87800427273902</v>
+        <v>84.14678715920773</v>
       </c>
       <c r="C14" t="n">
-        <v>39.58881916701641</v>
+        <v>41.74793752206669</v>
       </c>
       <c r="D14" t="n">
-        <v>1.522276394792464</v>
+        <v>1.721806785884074</v>
       </c>
       <c r="E14" t="n">
-        <v>12.08479059331865</v>
+        <v>11.38369025690204</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556496354914325</v>
+        <v>0.7489251805582506</v>
       </c>
       <c r="G14" t="n">
-        <v>25.27346278168701</v>
+        <v>27.9192847477789</v>
       </c>
       <c r="H14" t="n">
-        <v>36.50870843911535</v>
+        <v>36.13407735104427</v>
       </c>
       <c r="I14" t="n">
-        <v>3.01030620651267</v>
+        <v>1.558220458551125</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722810221821454</v>
+        <v>4.680782378489067</v>
       </c>
       <c r="K14" t="n">
-        <v>16.12199572726097</v>
+        <v>15.85321284079228</v>
       </c>
       <c r="L14" t="n">
-        <v>44.18896146338784</v>
+        <v>42.34694099646252</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89977635766522</v>
+        <v>99.9480913593215</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.26409779831938</v>
+        <v>83.37137336996246</v>
       </c>
       <c r="C15" t="n">
-        <v>39.44037101510781</v>
+        <v>41.18876755255613</v>
       </c>
       <c r="D15" t="n">
-        <v>1.499746469714273</v>
+        <v>1.68889196082499</v>
       </c>
       <c r="E15" t="n">
-        <v>12.32445222104976</v>
+        <v>11.38679558115116</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564092744640883</v>
+        <v>0.7493217280048217</v>
       </c>
       <c r="G15" t="n">
-        <v>24.89941164032677</v>
+        <v>27.38556727100869</v>
       </c>
       <c r="H15" t="n">
-        <v>36.54540988972035</v>
+        <v>36.15320993795645</v>
       </c>
       <c r="I15" t="n">
-        <v>2.511110337643606</v>
+        <v>1.324326090986199</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727557965400553</v>
+        <v>4.683260800030135</v>
       </c>
       <c r="K15" t="n">
-        <v>16.73590220168059</v>
+        <v>16.62862663003754</v>
       </c>
       <c r="L15" t="n">
-        <v>43.74010716636403</v>
+        <v>42.13848497586206</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91638038315243</v>
+        <v>99.95587915845573</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.9931386438098</v>
+        <v>81.20977109222889</v>
       </c>
       <c r="C16" t="n">
-        <v>37.55782577571797</v>
+        <v>39.23290844255971</v>
       </c>
       <c r="D16" t="n">
-        <v>1.413010248856844</v>
+        <v>1.599389088148126</v>
       </c>
       <c r="E16" t="n">
-        <v>11.96074675634103</v>
+        <v>10.96736959452928</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570612722130873</v>
+        <v>0.7496613135906854</v>
       </c>
       <c r="G16" t="n">
-        <v>23.45938100123691</v>
+        <v>25.93426843277898</v>
       </c>
       <c r="H16" t="n">
-        <v>36.57691072635568</v>
+        <v>36.1695942339388</v>
       </c>
       <c r="I16" t="n">
-        <v>2.094395687474436</v>
+        <v>1.104105219301234</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731632951331797</v>
+        <v>4.685383209941784</v>
       </c>
       <c r="K16" t="n">
-        <v>19.00686135619023</v>
+        <v>18.79022890777113</v>
       </c>
       <c r="L16" t="n">
-        <v>43.36555980315724</v>
+        <v>41.94007581380842</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93024693506544</v>
+        <v>99.96321316413925</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.72993868991577</v>
+        <v>85.45985507868374</v>
       </c>
       <c r="C17" t="n">
-        <v>38.82589319754166</v>
+        <v>42.06346382519069</v>
       </c>
       <c r="D17" t="n">
-        <v>1.414196434532794</v>
+        <v>1.600134773142592</v>
       </c>
       <c r="E17" t="n">
-        <v>12.76277724772996</v>
+        <v>12.4791364372325</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576968056337698</v>
+        <v>0.7500108290379388</v>
       </c>
       <c r="G17" t="n">
-        <v>23.92381604603753</v>
+        <v>27.25379308237968</v>
       </c>
       <c r="H17" t="n">
-        <v>37.05235759918541</v>
+        <v>37.49389091113427</v>
       </c>
       <c r="I17" t="n">
-        <v>2.083489521585248</v>
+        <v>1.19532136426965</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735605035211062</v>
+        <v>4.687567681487117</v>
       </c>
       <c r="K17" t="n">
-        <v>17.27006131008424</v>
+        <v>14.54014492131626</v>
       </c>
       <c r="L17" t="n">
-        <v>43.83465409394465</v>
+        <v>43.35656577589515</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93060860157055</v>
+        <v>99.9601745224021</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.54471556241799</v>
+        <v>87.02326866274272</v>
       </c>
       <c r="C18" t="n">
-        <v>36.9626369511009</v>
+        <v>42.78557605580396</v>
       </c>
       <c r="D18" t="n">
-        <v>1.334045534195381</v>
+        <v>1.601355344479404</v>
       </c>
       <c r="E18" t="n">
-        <v>12.32901657894365</v>
+        <v>13.06798117359747</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582416336034162</v>
+        <v>0.7505829319230128</v>
       </c>
       <c r="G18" t="n">
-        <v>22.56791148513397</v>
+        <v>27.39829313657587</v>
       </c>
       <c r="H18" t="n">
-        <v>37.07900039431306</v>
+        <v>37.52249098240314</v>
       </c>
       <c r="I18" t="n">
-        <v>1.737489726207169</v>
+        <v>1.991421769244982</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739010210021353</v>
+        <v>4.69114332451883</v>
       </c>
       <c r="K18" t="n">
-        <v>19.455284437582</v>
+        <v>12.9767313372573</v>
       </c>
       <c r="L18" t="n">
-        <v>43.52420390238417</v>
+        <v>44.17136247744463</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94212529106707</v>
+        <v>99.9336698705059</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.73839635544306</v>
+        <v>84.59392415110692</v>
       </c>
       <c r="C19" t="n">
-        <v>36.42421404243024</v>
+        <v>40.66545443177957</v>
       </c>
       <c r="D19" t="n">
-        <v>1.305146363294927</v>
+        <v>1.509866724348257</v>
       </c>
       <c r="E19" t="n">
-        <v>12.30339964221664</v>
+        <v>12.59814872188821</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587008557467614</v>
+        <v>0.75107407083885</v>
       </c>
       <c r="G19" t="n">
-        <v>22.07902717484798</v>
+        <v>25.83297408252863</v>
       </c>
       <c r="H19" t="n">
-        <v>37.10145695338282</v>
+        <v>37.54704357313871</v>
       </c>
       <c r="I19" t="n">
-        <v>1.448785017536665</v>
+        <v>1.660604035621463</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74188034841726</v>
+        <v>4.694212942742812</v>
       </c>
       <c r="K19" t="n">
-        <v>20.26160364455695</v>
+        <v>15.40607584889307</v>
       </c>
       <c r="L19" t="n">
-        <v>43.26591870950705</v>
+        <v>43.87315244795946</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95173639649423</v>
+        <v>99.9446827286321</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.2722559398521</v>
+        <v>81.9851259766119</v>
       </c>
       <c r="C20" t="n">
-        <v>34.18135376183991</v>
+        <v>38.31390487450077</v>
       </c>
       <c r="D20" t="n">
-        <v>1.215589116732603</v>
+        <v>1.412042264404669</v>
       </c>
       <c r="E20" t="n">
-        <v>11.6604832334501</v>
+        <v>12.01268232900068</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590961993086799</v>
+        <v>0.7514968910201938</v>
       </c>
       <c r="G20" t="n">
-        <v>20.56399641955232</v>
+        <v>24.1592523575526</v>
       </c>
       <c r="H20" t="n">
-        <v>37.12078976688002</v>
+        <v>37.56818083294957</v>
       </c>
       <c r="I20" t="n">
-        <v>1.207949958249114</v>
+        <v>1.384615732807967</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744351245679251</v>
+        <v>4.69685556887621</v>
       </c>
       <c r="K20" t="n">
-        <v>22.72774406014789</v>
+        <v>18.01487402338812</v>
       </c>
       <c r="L20" t="n">
-        <v>43.05065814974731</v>
+        <v>43.62509321223274</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95975597173512</v>
+        <v>99.95387211012162</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.75157640931737</v>
+        <v>79.21824678677899</v>
       </c>
       <c r="C21" t="n">
-        <v>37.53876546133581</v>
+        <v>35.76090239281305</v>
       </c>
       <c r="D21" t="n">
-        <v>1.216454548792373</v>
+        <v>1.308725115428319</v>
       </c>
       <c r="E21" t="n">
-        <v>13.48706023920883</v>
+        <v>11.32613239139859</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596366337188669</v>
+        <v>0.7518619303261108</v>
       </c>
       <c r="G21" t="n">
-        <v>22.10233955950336</v>
+        <v>22.39155379929814</v>
       </c>
       <c r="H21" t="n">
-        <v>38.67092042579823</v>
+        <v>37.58642956134711</v>
       </c>
       <c r="I21" t="n">
-        <v>1.767436041552783</v>
+        <v>1.154406924442537</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74772896074292</v>
+        <v>4.699137064538192</v>
       </c>
       <c r="K21" t="n">
-        <v>17.24842359068264</v>
+        <v>20.78175321322099</v>
       </c>
       <c r="L21" t="n">
-        <v>45.15393832730517</v>
+        <v>43.41888284583241</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94112737932362</v>
+        <v>99.96153845186646</v>
       </c>
     </row>
   </sheetData>
